--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -74,7 +74,7 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>付款方式</t>
+    <t>结算方式</t>
   </si>
   <si>
     <t>付款条件</t>
@@ -3326,6 +3326,14 @@
       <c r="U200" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R2:R1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576">
+      <formula1>"以""采购入库""数量,以""采购收货""数量,以""采购下单""数量"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <picture r:id="rId1"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -29,19 +29,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
-    <t>序号</t>
+    <t>*序号</t>
   </si>
   <si>
     <t>模具编号(供应商)</t>
   </si>
   <si>
-    <t>模具类型</t>
-  </si>
-  <si>
-    <t>模具穴数</t>
-  </si>
-  <si>
-    <t>产品名称</t>
+    <t>*模具类型</t>
+  </si>
+  <si>
+    <t>*模具穴数</t>
+  </si>
+  <si>
+    <t>*产品名称</t>
   </si>
   <si>
     <t>模具尺寸.长(cm)</t>
@@ -53,31 +53,31 @@
     <t>模具尺寸.高(cm)</t>
   </si>
   <si>
-    <t>模具材质</t>
-  </si>
-  <si>
-    <t>模具寿命(万)(啤)</t>
+    <t>*模具材质</t>
+  </si>
+  <si>
+    <t>*模具寿命(万)(啤)</t>
   </si>
   <si>
     <t>开模周期(自然日)</t>
   </si>
   <si>
-    <t>模具启用日期</t>
-  </si>
-  <si>
-    <t>数量(套)</t>
+    <t>*模具启用日期</t>
+  </si>
+  <si>
+    <t>*数量(套)</t>
   </si>
   <si>
     <t>含税单价(￥)</t>
   </si>
   <si>
-    <t>税率(%)</t>
-  </si>
-  <si>
-    <t>结算方式</t>
-  </si>
-  <si>
-    <t>付款条件</t>
+    <t>*税率(%)</t>
+  </si>
+  <si>
+    <t>*结算方式</t>
+  </si>
+  <si>
+    <t>*付款条件</t>
   </si>
   <si>
     <t>费用返还</t>
@@ -102,33 +102,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="10"/>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -136,14 +122,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -151,7 +137,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -159,7 +145,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -167,7 +153,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -175,7 +161,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -183,14 +169,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -198,7 +184,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -206,7 +192,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -214,14 +200,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -229,42 +215,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -571,20 +557,31 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,135 +590,123 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -776,7 +761,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -786,9 +985,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -802,38 +1001,38 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -866,9 +1065,9 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -898,66 +1097,40 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -971,20 +1144,38 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1042,93 +1233,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
+  <sheetPr/>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="13" max="23" width="14" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="22.75" customWidth="1"/>
+    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="22.625" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="11" max="11" width="18.625" customWidth="1"/>
+    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="19" max="19" width="14.25" customWidth="1"/>
+    <col min="20" max="20" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R$1:R$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1">
-      <formula1>"以""采购入库""数量,以""采购收货""数量,以""采购下单""数量"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576">
+      <formula1>"以""采购下单""数量,以""采购收货""数量,以""采购入库""数量"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <picture r:id="rId1"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -89,7 +89,7 @@
     <t>返还标准</t>
   </si>
   <si>
-    <t>返还单量</t>
+    <t>返还数量</t>
   </si>
 </sst>
 </file>

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -44,13 +44,13 @@
     <t>*产品名称</t>
   </si>
   <si>
-    <t>模具尺寸.长(cm)</t>
-  </si>
-  <si>
-    <t>模具尺寸.宽(cm)</t>
-  </si>
-  <si>
-    <t>模具尺寸.高(cm)</t>
+    <t>模具尺寸.长(mm)</t>
+  </si>
+  <si>
+    <t>模具尺寸.宽(mm)</t>
+  </si>
+  <si>
+    <t>模具尺寸.高(mm)</t>
   </si>
   <si>
     <t>*模具材质</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -68,7 +68,7 @@
     <t>*数量(套)</t>
   </si>
   <si>
-    <t>含税单价(￥)</t>
+    <t>*含税单价(￥)</t>
   </si>
   <si>
     <t>*税率(%)</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,11 +96,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -705,8 +706,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1246,7 +1250,7 @@
     <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="18.625" customWidth="1"/>
     <col min="11" max="11" width="18.625" customWidth="1"/>
-    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="12" max="12" width="19.375" style="1" customWidth="1"/>
     <col min="19" max="19" width="14.25" customWidth="1"/>
     <col min="20" max="20" width="15.875" customWidth="1"/>
   </cols>
@@ -1285,7 +1289,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>*序号</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>*模具启用日期</t>
+  </si>
+  <si>
+    <t>*模具供应商</t>
   </si>
   <si>
     <t>*数量(套)</t>
@@ -706,11 +709,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1238,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1251,11 +1257,12 @@
     <col min="9" max="9" width="18.625" customWidth="1"/>
     <col min="11" max="11" width="18.625" customWidth="1"/>
     <col min="12" max="12" width="19.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.25" customWidth="1"/>
-    <col min="20" max="20" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="19.375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="14.25" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1299,7 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1318,14 +1325,17 @@
       </c>
       <c r="U1" t="s">
         <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R$1:R$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S$1:S$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
       <formula1>"以""采购下单""数量,以""采购收货""数量,以""采购入库""数量"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/mouldDetailTemplate.xlsx
@@ -35,13 +35,13 @@
     <t>模具编号(供应商)</t>
   </si>
   <si>
+    <t>*产品名称</t>
+  </si>
+  <si>
     <t>*模具类型</t>
   </si>
   <si>
     <t>*模具穴数</t>
-  </si>
-  <si>
-    <t>*产品名称</t>
   </si>
   <si>
     <t>模具尺寸.长(mm)</t>
@@ -1247,10 +1247,9 @@
   <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="22.75" customWidth="1"/>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="22.75" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="14.25" customWidth="1"/>
     <col min="8" max="8" width="22.625" customWidth="1"/>
